--- a/samples/survey_leadership16.xlsx
+++ b/samples/survey_leadership16.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:AF34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,32 +441,147 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>팀을 이끄는 방법을 다룬 강의는 전반적으로 만족하셨습니까?</t>
+          <t>팀을 이끄는 방법을 다룬 강의 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[스트레스 관리 - 오푸름 강사] 강의 전반에 대해 얼마나 만족하십니까?</t>
+          <t>팀을 이끄는 방법을 다룬 강의 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[성인지 교육 - 오푸름 강사] 강의 전반에 대해 얼마나 만족하십니까?</t>
+          <t>팀을 이끄는 방법을 다룬 강의 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[공직가치 - 오푸름 강사] 강의 전반에 대해 얼마나 만족하십니까?</t>
+          <t>팀을 이끄는 방법을 다룬 강의 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>이번 과정에서 좋았던 점을 자유롭게 적어 주세요.</t>
+          <t>팀을 이끄는 방법을 다룬 강의 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>개선이 필요한 점을 자유롭게 적어 주세요.</t>
+          <t>스트레스 관리 | 오여름 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>스트레스 관리 | 오여름 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>스트레스 관리 | 오여름 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>스트레스 관리 | 오여름 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>스트레스 관리 | 오여름 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>성인지 교육 | 오푸름 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>성인지 교육 | 오푸름 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>성인지 교육 | 오푸름 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>성인지 교육 | 오푸름 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>성인지 교육 | 오푸름 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>공직가치 | 박로운 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>공직가치 | 박로운 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>공직가치 | 박로운 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>공직가치 | 박로운 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>공직가치 | 박로운 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>공통 | 교육시설환경 | 교재의 품질</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>공통 | 교육시설환경 | 강의실 및 교육기자재</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>공통 | 교육시설환경 | 편의시설</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>공통 | 교육시설환경 | 교직원의 친절도</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>공통 | 구내식당 | 구내식당 이용</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>공통 | 구내식당 | 음식의 간</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>공통 | 구내식당 | 메뉴의 다양성</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>공통 | 구내식당 | 청결도</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>공통 | 구내식당 | 친절도</t>
         </is>
       </c>
     </row>
@@ -478,7 +593,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -488,17 +603,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -509,7 +624,122 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>강의실이 더워서 집중하기 어려웠음</t>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>강사님이 열정적으로 진행해 주셨음</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
         </is>
       </c>
     </row>
@@ -521,27 +751,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -551,10 +781,125 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>성인지 교육 강의: 최신 법령 개정 내용을 알려 주어 실무에 도움이 됨</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>강의실 의자가 불편했음</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>실습 시간이 부족했음</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>강의실이 더워서 집중하기 어려웠음</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -569,35 +914,138 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>공직가치 강의: 사례가 조금 더 있으면 좋겠음</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>이론 비중이 높아 실무 내용이 더 필요함</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -607,7 +1055,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -617,7 +1065,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -635,14 +1083,113 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>리더십과 소통 강의: 질문에 성실하게 답변해 주셔서 좋았음</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>스트레스 관리 강의: 설명 속도가 빨라 따라가기 어려웠음</t>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>만족</t>
         </is>
       </c>
     </row>
@@ -654,22 +1201,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -679,15 +1226,118 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>과정 전체 일정 구성이 알찼음</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -697,12 +1347,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -712,12 +1362,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -725,8 +1375,127 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>최신 법령 개정 내용을 알려 주어 실무에 도움이 됨</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>교구가 부족해 기다리는 시간이 길었음</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>사례가 조금 더 있으면 좋겠음</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>핵심만 짚어 주어 집중이 잘 됐음</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -741,17 +1510,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -761,17 +1530,116 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>성인지 교육 강의: 강사님이 열정적으로 진행해 주셨음</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>강의실 의자가 불편했음</t>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>만족</t>
         </is>
       </c>
     </row>
@@ -788,7 +1656,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>소방교</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -798,7 +1666,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -814,7 +1682,114 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>공직가치 강의: 사례가 조금 더 있으면 좋겠음</t>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>핵심만 짚어 주어 집중이 잘 됐음</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
         </is>
       </c>
     </row>
@@ -826,17 +1801,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -846,22 +1821,121 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>리더십과 소통 강의: 실습 장비가 충분해서 직접 해 볼 수 있었음</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>강의실 의자가 불편했음</t>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>마이크 소리가 작아 뒷자리에서 잘 안 들렸음</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>만족</t>
         </is>
       </c>
     </row>
@@ -873,12 +1947,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방교</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -888,12 +1962,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -903,12 +1977,111 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>스트레스 관리 강의: 핵심만 짚어 주어 집중이 잘 됐음</t>
+          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>성인지 교육 강의: 자료 글씨가 작아 화면이 잘 안 보였음</t>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>사례가 조금 더 있으면 좋겠음</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>만족</t>
         </is>
       </c>
     </row>
@@ -920,12 +2093,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>소방본부</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -940,18 +2113,121 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>스트레스 관리 강의: 점심 직후 시간이라 집중이 어려웠음, 시간 조정 필요</t>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>불만족</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
         </is>
       </c>
     </row>
@@ -963,12 +2239,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -983,7 +2259,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -994,9 +2270,112 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>성인지 교육 강의: 점심 직후 시간이라 집중이 어려웠음, 시간 조정 필요</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>강의실 의자가 불편했음</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1006,7 +2385,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1021,7 +2400,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1034,10 +2413,117 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>실습 순서를 단계별로 알려 주어 따라가기 쉬웠음</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>성인지 교육 강의: 교구가 부족해 기다리는 시간이 길었음</t>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
         </is>
       </c>
     </row>
@@ -1049,7 +2535,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>소방본부</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1064,7 +2550,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1074,13 +2560,124 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>마이크 소리가 작아 뒷자리에서 잘 안 들렸음</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>식당 대기 시간이 길었음</t>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>사례가 조금 더 있으면 좋겠음</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
         </is>
       </c>
     </row>
@@ -1097,12 +2694,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>소방교</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1112,16 +2709,131 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>이론 비중이 높아 실무 내용이 더 필요함</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>교육 운영 안내가 미리 와서 준비하기 좋았음</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1131,27 +2843,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1159,14 +2871,113 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>과정 전체 일정 구성이 알찼음</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>성인지 교육 강의: 교구가 부족해 기다리는 시간이 길었음</t>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>불만족</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>최신 법령 개정 내용을 알려 주어 실무에 도움이 됨</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>만족</t>
         </is>
       </c>
     </row>
@@ -1178,12 +2989,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1193,7 +3004,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1209,7 +3020,110 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>공직가치 강의: 점심 직후 시간이라 집중이 어려웠음, 시간 조정 필요</t>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>불만족</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>자료가 깔끔하게 정리되어 복습하기 좋았음</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>만족</t>
         </is>
       </c>
     </row>
@@ -1221,17 +3135,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1246,17 +3160,124 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>성인지 교육 강의: 강사님이 열정적으로 진행해 주셨음</t>
+          <t>핵심만 짚어 주어 집중이 잘 됐음</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>성인지 교육 강의: 교구가 부족해 기다리는 시간이 길었음</t>
+          <t>불만족</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>사례가 조금 더 있으면 좋겠음</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>만족</t>
         </is>
       </c>
     </row>
@@ -1268,12 +3289,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1283,7 +3304,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1296,14 +3317,117 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>교육 운영 안내가 미리 와서 준비하기 좋았음</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>스트레스 관리 강의: 설명 속도가 빨라 따라가기 어려웠음</t>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>마이크 소리가 작아 뒷자리에서 잘 안 들렸음</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
         </is>
       </c>
     </row>
@@ -1315,17 +3439,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방교</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1345,12 +3469,115 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>스트레스 관리 강의: 질문에 성실하게 답변해 주셔서 좋았음</t>
+          <t>교육 운영 안내가 미리 와서 준비하기 좋았음</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>스트레스 관리 강의: 사례가 조금 더 있으면 좋겠음</t>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
         </is>
       </c>
     </row>
@@ -1362,7 +3589,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>소방본부</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1377,12 +3604,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1392,12 +3619,115 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>성인지 교육 강의: 핵심만 짚어 주어 집중이 잘 됐음</t>
+          <t>핵심만 짚어 주어 집중이 잘 됐음</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>식당 대기 시간이 길었음</t>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
         </is>
       </c>
     </row>
@@ -1414,17 +3744,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1434,13 +3764,124 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>핵심만 짚어 주어 집중이 잘 됐음</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>스트레스 관리 강의: 사례가 조금 더 있으면 좋겠음</t>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>자료가 깔끔하게 정리되어 복습하기 좋았음</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
         </is>
       </c>
     </row>
@@ -1452,17 +3893,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>소방본부</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1477,17 +3918,120 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>성인지 교육 강의: 자료가 깔끔하게 정리되어 복습하기 좋았음</t>
+          <t>최신 법령 개정 내용을 알려 주어 실무에 도움이 됨</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>숙소 와이파이가 자주 끊김</t>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>만족</t>
         </is>
       </c>
     </row>
@@ -1499,12 +4043,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방교</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1524,15 +4068,114 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>공직가치 강의: 핵심만 짚어 주어 집중이 잘 됐음</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1542,42 +4185,1207 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>소방본부</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>소방사</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>강사님이 열정적으로 진행해 주셨음</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026/10/21 오후 05:15:00</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>소방본부</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>소방장</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026/10/21 오후 05:18:00</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>△△소방서</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>소방장</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>강의실이 더워서 집중하기 어려웠음</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>불만족</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026/10/21 오후 05:21:00</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>△△소방서</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>소방교</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>불만족</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>불만족</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>강사님이 열정적으로 진행해 주셨음</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>교육 운영 안내가 미리 와서 준비하기 좋았음</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026/10/21 오후 05:24:00</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>△△소방서</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>소방위</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>교육 운영 안내가 미리 와서 준비하기 좋았음</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026/10/21 오후 05:27:00</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>소방본부</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>소방사</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>설명 속도가 빨라 따라가기 어려웠음</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>핵심만 짚어 주어 집중이 잘 됐음</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026/10/21 오후 05:30:00</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>□□소방서</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>소방위</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>실습 순서를 단계별로 알려 주어 따라가기 쉬웠음</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026/10/21 오후 05:33:00</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>소방본부</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>소방사</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>성인지 교육 강의: 질문에 성실하게 답변해 주셔서 좋았음</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>강의실 의자가 불편했음</t>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>사례가 조금 더 있으면 좋겠음</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>이론 비중이 높아 실무 내용이 더 필요함</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>자료가 깔끔하게 정리되어 복습하기 좋았음</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
         </is>
       </c>
     </row>

--- a/samples/survey_leadership16.xlsx
+++ b/samples/survey_leadership16.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF34"/>
+  <dimension ref="A1:AG34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,6 +584,11 @@
           <t>공통 | 구내식당 | 친절도</t>
         </is>
       </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>공통 | 과정 운영 | 의견: 이번 과정 운영(일정·시설·안내 등)에 대한 의견을 자유롭게 적어 주세요(선택)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -742,6 +747,11 @@
           <t>매우 만족</t>
         </is>
       </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>마이크 소리가 작아 뒷자리에서 잘 안 들렸음</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -751,12 +761,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>소방교</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -779,11 +789,7 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>강의실 의자가 불편했음</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>만족</t>
@@ -804,7 +810,11 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>실습 시간이 부족했음</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -825,11 +835,7 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>실습 시간이 부족했음</t>
-        </is>
-      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -852,7 +858,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>강의실이 더워서 집중하기 어려웠음</t>
+          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -900,6 +906,7 @@
           <t>매우 만족</t>
         </is>
       </c>
+      <c r="AG4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1046,6 +1053,11 @@
         </is>
       </c>
       <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>마이크 소리가 작아 뒷자리에서 잘 안 들렸음</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1055,12 +1067,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1104,7 +1116,11 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>실습 순서를 단계별로 알려 주어 따라가기 쉬웠음</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1192,6 +1208,7 @@
           <t>만족</t>
         </is>
       </c>
+      <c r="AG6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1201,12 +1218,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1229,7 +1246,11 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>실습 시간이 부족했음</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1292,7 +1313,11 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>최신 법령 개정 내용을 알려 주어 실무에 도움이 됨</t>
+        </is>
+      </c>
       <c r="X7" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1323,11 +1348,7 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -1336,6 +1357,11 @@
       <c r="AF7" t="inlineStr">
         <is>
           <t>만족</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>주차 공간이 부족했음</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1373,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1377,34 +1403,34 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>강의실이 더워서 집중하기 어려웠음</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>최신 법령 개정 내용을 알려 주어 실무에 도움이 됨</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>교구가 부족해 기다리는 시간이 길었음</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1425,11 +1451,7 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>사례가 조금 더 있으면 좋겠음</t>
-        </is>
-      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -1450,11 +1472,7 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>핵심만 짚어 주어 집중이 잘 됐음</t>
-        </is>
-      </c>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1480,7 +1498,11 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1496,6 +1518,7 @@
           <t>매우 만족</t>
         </is>
       </c>
+      <c r="AG8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1505,7 +1528,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1554,7 +1577,11 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>강의실 의자가 불편했음</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -1575,7 +1602,11 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>설명 속도가 빨라 따라가기 어려웠음</t>
+        </is>
+      </c>
       <c r="S9" t="inlineStr">
         <is>
           <t>보통</t>
@@ -1622,11 +1653,7 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -1642,6 +1669,7 @@
           <t>만족</t>
         </is>
       </c>
+      <c r="AG9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1651,12 +1679,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1742,11 +1770,7 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>핵심만 짚어 주어 집중이 잘 됐음</t>
-        </is>
-      </c>
+      <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -1792,6 +1816,7 @@
           <t>매우 만족</t>
         </is>
       </c>
+      <c r="AG10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1801,7 +1826,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1894,7 +1919,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>마이크 소리가 작아 뒷자리에서 잘 안 들렸음</t>
+          <t>실습 순서를 단계별로 알려 주어 따라가기 쉬웠음</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -1927,7 +1952,11 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
       <c r="AE11" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1936,6 +1965,11 @@
       <c r="AF11" t="inlineStr">
         <is>
           <t>만족</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>식당 대기 시간이 길었음</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1981,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2000,11 +2034,7 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>사례가 조금 더 있으면 좋겠음</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2072,18 +2102,27 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
       <c r="AF12" t="inlineStr">
         <is>
           <t>만족</t>
         </is>
       </c>
+      <c r="AG12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2093,12 +2132,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2163,7 +2202,11 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
+        </is>
+      </c>
       <c r="S13" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2225,9 +2268,10 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>과정 전체 일정 구성이 알찼음</t>
         </is>
       </c>
     </row>
@@ -2239,12 +2283,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방교</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2267,7 +2311,11 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>강사님이 열정적으로 진행해 주셨음</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>보통</t>
@@ -2311,7 +2359,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
+          <t>자료가 깔끔하게 정리되어 복습하기 좋았음</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2334,11 +2382,7 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>강의실 의자가 불편했음</t>
-        </is>
-      </c>
+      <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2374,8 +2418,17 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2385,12 +2438,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2415,7 +2468,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>실습 순서를 단계별로 알려 주어 따라가기 쉬웠음</t>
+          <t>사례가 조금 더 있으면 좋겠음</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2459,7 +2512,11 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2511,11 +2568,7 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2526,6 +2579,7 @@
           <t>매우 만족</t>
         </is>
       </c>
+      <c r="AG15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2540,7 +2594,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2563,11 +2617,7 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>마이크 소리가 작아 뒷자리에서 잘 안 들렸음</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2588,11 +2638,7 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>사례가 조금 더 있으면 좋겠음</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2634,11 +2680,7 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
-        </is>
-      </c>
+      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2674,12 +2716,17 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
       <c r="AF16" t="inlineStr">
         <is>
           <t>매우 만족</t>
         </is>
       </c>
+      <c r="AG16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2689,12 +2736,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2717,7 +2764,11 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2738,11 +2789,7 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>이론 비중이 높아 실무 내용이 더 필요함</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2784,11 +2831,7 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>교육 운영 안내가 미리 와서 준비하기 좋았음</t>
-        </is>
-      </c>
+      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2814,11 +2857,7 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2834,6 +2873,7 @@
           <t>만족</t>
         </is>
       </c>
+      <c r="AG17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2843,12 +2883,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>소방본부</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2892,11 +2932,7 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>최신 법령 개정 내용을 알려 주어 실무에 도움이 됨</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>보통</t>
@@ -2938,7 +2974,11 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>자료가 깔끔하게 정리되어 복습하기 좋았음</t>
+        </is>
+      </c>
       <c r="X18" t="inlineStr">
         <is>
           <t>보통</t>
@@ -2959,12 +2999,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
       <c r="AD18" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2980,6 +3020,7 @@
           <t>만족</t>
         </is>
       </c>
+      <c r="AG18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2989,12 +3030,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3017,7 +3058,11 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>점심 직후 시간이라 집중이 어려웠음, 시간 조정 필요</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3059,7 +3104,11 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>실습 시간이 부족했음</t>
+        </is>
+      </c>
       <c r="S19" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -3080,11 +3129,7 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>자료가 깔끔하게 정리되어 복습하기 좋았음</t>
-        </is>
-      </c>
+      <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -3105,7 +3150,11 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -3116,14 +3165,15 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
           <t>만족</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>강의실 의자가 불편했음</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3190,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3163,11 +3213,7 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>핵심만 짚어 주어 집중이 잘 됐음</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>불만족</t>
@@ -3209,7 +3255,11 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>최신 법령 개정 내용을 알려 주어 실무에 도움이 됨</t>
+        </is>
+      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3230,11 +3280,7 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>사례가 조금 더 있으면 좋겠음</t>
-        </is>
-      </c>
+      <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
           <t>보통</t>
@@ -3278,6 +3324,11 @@
       <c r="AF20" t="inlineStr">
         <is>
           <t>만족</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>강의실 의자가 불편했음</t>
         </is>
       </c>
     </row>
@@ -3289,12 +3340,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방교</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3359,11 +3410,7 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>마이크 소리가 작아 뒷자리에서 잘 안 들렸음</t>
-        </is>
-      </c>
+      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -3384,7 +3431,11 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>점심 직후 시간이라 집중이 어려웠음, 시간 조정 필요</t>
+        </is>
+      </c>
       <c r="X21" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -3430,6 +3481,7 @@
           <t>매우 만족</t>
         </is>
       </c>
+      <c r="AG21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3444,7 +3496,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3469,7 +3521,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>교육 운영 안내가 미리 와서 준비하기 좋았음</t>
+          <t>핵심만 짚어 주어 집중이 잘 됐음</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3578,6 +3630,11 @@
       <c r="AF22" t="inlineStr">
         <is>
           <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>식당 대기 시간이 길었음</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3646,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3619,7 +3676,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>핵심만 짚어 주어 집중이 잘 됐음</t>
+          <t>자료가 깔끔하게 정리되어 복습하기 좋았음</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3730,6 +3787,7 @@
           <t>매우 만족</t>
         </is>
       </c>
+      <c r="AG23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3744,7 +3802,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3767,11 +3825,7 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>핵심만 짚어 주어 집중이 잘 됐음</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3792,11 +3846,7 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>자료가 깔끔하게 정리되어 복습하기 좋았음</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -3884,6 +3934,7 @@
           <t>매우 만족</t>
         </is>
       </c>
+      <c r="AG24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3898,7 +3949,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3923,7 +3974,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>최신 법령 개정 내용을 알려 주어 실무에 도움이 됨</t>
+          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3988,7 +4039,11 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>실습 순서를 단계별로 알려 주어 따라가기 쉬웠음</t>
+        </is>
+      </c>
       <c r="X25" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4014,11 +4069,7 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4029,9 +4080,10 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>만족</t>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>식당 대기 시간이 길었음</t>
         </is>
       </c>
     </row>
@@ -4043,12 +4095,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4134,7 +4186,11 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>최신 법령 개정 내용을 알려 주어 실무에 도움이 됨</t>
+        </is>
+      </c>
       <c r="X26" t="inlineStr">
         <is>
           <t>보통</t>
@@ -4165,7 +4221,11 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
       <c r="AE26" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4176,6 +4236,7 @@
           <t>만족</t>
         </is>
       </c>
+      <c r="AG26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4190,7 +4251,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방교</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4234,11 +4295,7 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>강사님이 열정적으로 진행해 주셨음</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4301,21 +4358,13 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4326,6 +4375,7 @@
           <t>매우 만족</t>
         </is>
       </c>
+      <c r="AG27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4335,12 +4385,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>소방본부</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4405,7 +4455,11 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
+        </is>
+      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4426,7 +4480,11 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr"/>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>사례가 조금 더 있으면 좋겠음</t>
+        </is>
+      </c>
       <c r="X28" t="inlineStr">
         <is>
           <t>보통</t>
@@ -4472,6 +4530,7 @@
           <t>보통</t>
         </is>
       </c>
+      <c r="AG28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4481,12 +4540,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4509,7 +4568,11 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>마이크 소리가 작아 뒷자리에서 잘 안 들렸음</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4530,11 +4593,7 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4576,11 +4635,7 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>강의실이 더워서 집중하기 어려웠음</t>
-        </is>
-      </c>
+      <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr">
         <is>
           <t>보통</t>
@@ -4624,6 +4679,11 @@
       <c r="AF29" t="inlineStr">
         <is>
           <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>현장 실습과 이론 비율이 적절했음</t>
         </is>
       </c>
     </row>
@@ -4635,12 +4695,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4705,11 +4765,7 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>강사님이 열정적으로 진행해 주셨음</t>
-        </is>
-      </c>
+      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4730,11 +4786,7 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>교육 운영 안내가 미리 와서 준비하기 좋았음</t>
-        </is>
-      </c>
+      <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr">
         <is>
           <t>보통</t>
@@ -4780,6 +4832,7 @@
           <t>매우 만족</t>
         </is>
       </c>
+      <c r="AG30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4789,12 +4842,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4838,7 +4891,11 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>핵심만 짚어 주어 집중이 잘 됐음</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4859,11 +4916,7 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>교육 운영 안내가 미리 와서 준비하기 좋았음</t>
-        </is>
-      </c>
+      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4930,6 +4983,7 @@
           <t>만족</t>
         </is>
       </c>
+      <c r="AG31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4939,12 +4993,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>소방본부</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4988,11 +5042,7 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>설명 속도가 빨라 따라가기 어려웠음</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5013,11 +5063,7 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>핵심만 짚어 주어 집중이 잘 됐음</t>
-        </is>
-      </c>
+      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5074,16 +5120,13 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
           <t>만족</t>
         </is>
       </c>
+      <c r="AG32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5093,12 +5136,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방교</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5163,7 +5206,11 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>이론 비중이 높아 실무 내용이 더 필요함</t>
+        </is>
+      </c>
       <c r="S33" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -5186,7 +5233,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>실습 순서를 단계별로 알려 주어 따라가기 쉬웠음</t>
+          <t>자료가 깔끔하게 정리되어 복습하기 좋았음</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -5229,7 +5276,16 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AF33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>과정 전체 일정 구성이 알찼음</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5244,7 +5300,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5269,7 +5325,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>사례가 조금 더 있으면 좋겠음</t>
+          <t>강사님이 열정적으로 진행해 주셨음</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -5313,11 +5369,7 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>이론 비중이 높아 실무 내용이 더 필요함</t>
-        </is>
-      </c>
+      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5383,9 +5435,10 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>교육생 질문에 담당자가 빠르게 답해 주었음</t>
         </is>
       </c>
     </row>

--- a/samples/survey_leadership16.xlsx
+++ b/samples/survey_leadership16.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG34"/>
+  <dimension ref="A1:AG35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,77 +466,77 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>스트레스 관리 | 오여름 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
+          <t>스트레스 관리 | 이우람 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>스트레스 관리 | 오여름 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
+          <t>스트레스 관리 | 이우람 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>스트레스 관리 | 오여름 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
+          <t>스트레스 관리 | 이우람 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>스트레스 관리 | 오여름 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
+          <t>스트레스 관리 | 이우람 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>스트레스 관리 | 오여름 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
+          <t>스트레스 관리 | 이우람 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>성인지 교육 | 오푸름 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
+          <t>성인지 교육 | 이나래 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>성인지 교육 | 오푸름 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
+          <t>성인지 교육 | 이나래 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>성인지 교육 | 오푸름 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
+          <t>성인지 교육 | 이나래 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>성인지 교육 | 오푸름 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
+          <t>성인지 교육 | 이나래 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>성인지 교육 | 오푸름 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
+          <t>성인지 교육 | 이나래 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>공직가치 | 박로운 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
+          <t>공직가치 | 박바다 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>공직가치 | 박로운 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
+          <t>공직가치 | 박바다 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>공직가치 | 박로운 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
+          <t>공직가치 | 박바다 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>공직가치 | 박로운 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
+          <t>공직가치 | 박바다 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>공직가치 | 박로운 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
+          <t>공직가치 | 박바다 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -598,12 +598,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -629,12 +629,12 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>강사님이 열정적으로 진행해 주셨음</t>
+          <t>설명 속도가 빨라 따라가기 어려웠음</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -669,12 +669,12 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
+          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -689,27 +689,27 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
+          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -719,37 +719,37 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>마이크 소리가 작아 뒷자리에서 잘 안 들렸음</t>
+          <t>강의실 의자가 불편했음</t>
         </is>
       </c>
     </row>
@@ -761,12 +761,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>소방본부</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -792,7 +792,7 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -807,14 +807,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>실습 시간이 부족했음</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -822,7 +818,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -832,13 +828,13 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -858,7 +854,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
+          <t>강사님이 열정적으로 진행해 주셨음</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -873,7 +869,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -883,7 +879,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -898,15 +894,15 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>교육생 질문에 담당자가 빠르게 답해 주었음</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -916,7 +912,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -936,12 +932,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -952,12 +948,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -973,7 +969,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1007,19 +1003,15 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>이론 비중이 높아 실무 내용이 더 필요함</t>
-        </is>
-      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1032,19 +1024,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1052,10 +1040,14 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>마이크 소리가 작아 뒷자리에서 잘 안 들렸음</t>
+          <t>강의실 의자가 불편했음</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방교</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1087,12 +1079,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -1103,22 +1095,22 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>실습 순서를 단계별로 알려 주어 따라가기 쉬웠음</t>
+          <t>사례가 조금 더 있으면 좋겠음</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1128,7 +1120,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1144,25 +1136,29 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>점심 직후 시간이라 집중이 어려웠음, 시간 조정 필요</t>
+        </is>
+      </c>
       <c r="X6" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1190,7 +1186,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1205,10 +1201,14 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>쉬는 시간이 짧아 이동하기 바빴음</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1218,68 +1218,64 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>실습 시간이 부족했음</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1292,20 +1288,24 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>실습 시간이 부족했음</t>
+        </is>
+      </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>최신 법령 개정 내용을 알려 주어 실무에 도움이 됨</t>
+          <t>교구가 부족해 기다리는 시간이 길었음</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,13 +1345,17 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1361,7 +1365,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>주차 공간이 부족했음</t>
+          <t>강의실 의자가 불편했음</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1382,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1398,12 +1402,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>강의실이 더워서 집중하기 어려웠음</t>
+          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1413,32 +1417,28 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>최신 법령 개정 내용을 알려 주어 실무에 도움이 됨</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1448,31 +1448,35 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>점심 직후 시간이라 집중이 어려웠음, 시간 조정 필요</t>
+        </is>
+      </c>
       <c r="X8" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1485,22 +1489,18 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -1510,15 +1510,19 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>과정 전체 일정 구성이 알찼음</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1528,22 +1532,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1553,23 +1557,23 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1577,14 +1581,10 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>강의실 의자가 불편했음</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1602,14 +1602,10 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>설명 속도가 빨라 따라가기 어려웠음</t>
-        </is>
-      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1624,7 +1620,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
@@ -1635,17 +1631,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1653,10 +1649,14 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -1664,11 +1664,7 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1679,7 +1675,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1689,22 +1685,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -1715,12 +1711,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1731,7 +1727,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1741,39 +1737,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>이론 비중이 높아 실무 내용이 더 필요함</t>
+        </is>
+      </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -1813,10 +1813,14 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>강의실 의자가 불편했음</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1826,12 +1830,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>소방교</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1841,12 +1845,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1857,7 +1861,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1867,12 +1871,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1883,48 +1887,48 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>설명 속도가 빨라 따라가기 어려웠음</t>
+        </is>
+      </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>실습 순서를 단계별로 알려 주어 따라가기 쉬웠음</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1934,22 +1938,22 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -1967,11 +1971,7 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>식당 대기 시간이 길었음</t>
-        </is>
-      </c>
+      <c r="AG11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2001,22 +2001,22 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
+          <t>자료 글씨가 작아 화면이 잘 안 보였음</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2037,7 +2037,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2047,18 +2047,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>설명 속도가 빨라 따라가기 어려웠음</t>
+        </is>
+      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -2073,23 +2077,27 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
+        </is>
+      </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2109,20 +2117,20 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr"/>
+          <t>불만족</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>식당 대기 시간이 길었음</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2132,59 +2140,59 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>불만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2194,7 +2202,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2209,7 +2217,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -2224,10 +2232,14 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr"/>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>교구가 부족해 기다리는 시간이 길었음</t>
+        </is>
+      </c>
       <c r="X13" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2235,45 +2247,45 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>과정 전체 일정 구성이 알찼음</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2288,12 +2300,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2303,7 +2315,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2311,19 +2323,15 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>강사님이 열정적으로 진행해 주셨음</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2333,7 +2341,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -2344,27 +2352,27 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>자료가 깔끔하게 정리되어 복습하기 좋았음</t>
+          <t>이론 비중이 높아 실무 내용이 더 필요함</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -2374,18 +2382,18 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2395,12 +2403,12 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2415,12 +2423,12 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2428,7 +2436,11 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>쉬는 시간이 짧아 이동하기 바빴음</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2448,12 +2460,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2463,84 +2475,84 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>실습 순서를 단계별로 알려 주어 따라가기 쉬웠음</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>사례가 조금 더 있으면 좋겠음</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2560,7 +2572,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2568,18 +2580,26 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr"/>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>강의실이 더워서 집중하기 어려웠음</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2589,43 +2609,43 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2635,18 +2655,18 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2656,18 +2676,18 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2677,7 +2697,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="W16" t="inlineStr"/>
@@ -2688,22 +2708,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2711,19 +2731,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr"/>
@@ -2736,22 +2752,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>소방본부</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2761,14 +2777,10 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2776,7 +2788,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2786,7 +2798,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -2797,12 +2809,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2823,18 +2835,18 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2849,7 +2861,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2857,23 +2869,31 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>교육 운영 안내가 미리 와서 준비하기 좋았음</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2883,12 +2903,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방교</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2903,39 +2923,39 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>불만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2945,23 +2965,23 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2971,22 +2991,22 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>자료가 깔끔하게 정리되어 복습하기 좋았음</t>
+          <t>강의실이 더워서 집중하기 어려웠음</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2999,7 +3019,11 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3007,12 +3031,12 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -3020,7 +3044,11 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>강의실 의자가 불편했음</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3030,47 +3058,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>점심 직후 시간이라 집중이 어려웠음, 시간 조정 필요</t>
+          <t>실습 장비가 충분해서 직접 해 볼 수 있었음</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>불만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -3086,12 +3114,12 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3101,17 +3129,13 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>실습 시간이 부족했음</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -3126,23 +3150,23 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3165,10 +3189,14 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -3185,7 +3213,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3195,12 +3223,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3210,18 +3238,22 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>최신 법령 개정 내용을 알려 주어 실무에 도움이 됨</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>불만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3234,15 +3266,19 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>실습 시간이 부족했음</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3255,11 +3291,7 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>최신 법령 개정 내용을 알려 주어 실무에 도움이 됨</t>
-        </is>
-      </c>
+      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3272,7 +3304,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -3283,7 +3315,7 @@
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -3293,19 +3325,15 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -3318,19 +3346,15 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>강의실 의자가 불편했음</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3340,35 +3364,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>핵심만 짚어 주어 집중이 잘 됐음</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3381,12 +3409,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -3402,7 +3430,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -3410,10 +3438,14 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>강사님이 열정적으로 진행해 주셨음</t>
+        </is>
+      </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -3423,19 +3455,15 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>점심 직후 시간이라 집중이 어려웠음, 시간 조정 필요</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -3448,27 +3476,27 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
@@ -3478,7 +3506,7 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr"/>
@@ -3491,27 +3519,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3519,14 +3547,10 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>핵심만 짚어 주어 집중이 잘 됐음</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3541,7 +3565,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -3552,7 +3576,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3565,20 +3589,24 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>자료가 깔끔하게 정리되어 복습하기 좋았음</t>
+        </is>
+      </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -3589,17 +3617,17 @@
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3609,12 +3637,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -3629,14 +3657,10 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>식당 대기 시간이 길었음</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3646,12 +3670,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3661,7 +3685,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3676,7 +3700,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>자료가 깔끔하게 정리되어 복습하기 좋았음</t>
+          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3691,23 +3715,23 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3717,10 +3741,14 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>강의실 의자가 불편했음</t>
+        </is>
+      </c>
       <c r="S23" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3728,7 +3756,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3754,17 +3782,17 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3784,10 +3812,14 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AG23" t="inlineStr"/>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>과정 전체 일정 구성이 알찼음</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3802,7 +3834,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>소방교</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3812,7 +3844,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3828,12 +3860,12 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3843,18 +3875,18 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3875,12 +3907,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>불만족</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -3906,22 +3938,18 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
@@ -3931,10 +3959,14 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AG24" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>현장 실습과 이론 비율이 적절했음</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3944,7 +3976,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3954,12 +3986,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3969,17 +4001,13 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3989,7 +4017,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -4010,7 +4038,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -4021,7 +4049,7 @@
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -4036,17 +4064,17 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>실습 순서를 단계별로 알려 주어 따라가기 쉬웠음</t>
+          <t>점심 직후 시간이라 집중이 어려웠음, 시간 조정 필요</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -4061,29 +4089,33 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>식당 대기 시간이 길었음</t>
+          <t>강의실 의자가 불편했음</t>
         </is>
       </c>
     </row>
@@ -4095,59 +4127,63 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>소방본부</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방장</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>실습 장비가 충분해서 직접 해 볼 수 있었음</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -4168,7 +4204,7 @@
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -4178,12 +4214,12 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -4198,7 +4234,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -4218,7 +4254,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -4228,7 +4264,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -4256,12 +4292,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4271,23 +4307,23 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -4295,10 +4331,14 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>설명 속도가 빨라 따라가기 어려웠음</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -4313,13 +4353,13 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -4340,17 +4380,17 @@
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4358,24 +4398,32 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AG27" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>과정 전체 일정 구성이 알찼음</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4385,12 +4433,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방교</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4400,7 +4448,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4416,7 +4464,7 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4426,28 +4474,28 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -4455,11 +4503,7 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
-        </is>
-      </c>
+      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4467,12 +4511,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -4480,44 +4524,40 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>사례가 조금 더 있으면 좋겠음</t>
-        </is>
-      </c>
+      <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
@@ -4527,7 +4567,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr"/>
@@ -4540,17 +4580,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4560,22 +4600,18 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>마이크 소리가 작아 뒷자리에서 잘 안 들렸음</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4585,15 +4621,19 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>실습 순서를 단계별로 알려 주어 따라가기 쉬웠음</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4601,7 +4641,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4622,23 +4662,23 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -4658,12 +4698,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>불만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -4673,19 +4713,15 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>현장 실습과 이론 비율이 적절했음</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4695,17 +4731,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>소방본부</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>소방사</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4723,7 +4759,11 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>최신 법령 개정 내용을 알려 주어 실무에 도움이 됨</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4731,12 +4771,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>불만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>불만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -4744,15 +4784,19 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>설명 속도가 빨라 따라가기 어려웠음</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4765,36 +4809,40 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
+        </is>
+      </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -4809,12 +4857,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -4824,12 +4872,12 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr"/>
@@ -4842,12 +4890,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>□□소방서</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>소방위</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4867,13 +4915,13 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4883,7 +4931,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -4893,17 +4941,17 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>핵심만 짚어 주어 집중이 잘 됐음</t>
+          <t>강의실 의자가 불편했음</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4916,7 +4964,11 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>최신 법령 개정 내용을 알려 주어 실무에 도움이 됨</t>
+        </is>
+      </c>
       <c r="S31" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4934,10 +4986,14 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>실습 시간이 부족했음</t>
+        </is>
+      </c>
       <c r="X31" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4950,17 +5006,17 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4975,7 +5031,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -4983,7 +5039,11 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AG31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>강의실 의자가 불편했음</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4993,12 +5053,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>○○소방서</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방교</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5008,23 +5068,27 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -5034,36 +5098,44 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>자료가 깔끔하게 정리되어 복습하기 좋았음</t>
+        </is>
+      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5081,13 +5153,13 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -5102,12 +5174,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5117,16 +5189,24 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr"/>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AG32" t="inlineStr"/>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>쉬는 시간이 짧아 이동하기 바빴음</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5136,7 +5216,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방본부</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5151,12 +5231,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -5167,7 +5247,7 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -5177,12 +5257,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
@@ -5193,12 +5273,12 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -5206,19 +5286,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>이론 비중이 높아 실무 내용이 더 필요함</t>
-        </is>
-      </c>
+      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -5231,11 +5307,7 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>자료가 깔끔하게 정리되어 복습하기 좋았음</t>
-        </is>
-      </c>
+      <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5243,12 +5315,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5263,7 +5335,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
@@ -5281,11 +5353,7 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AG33" t="inlineStr">
-        <is>
-          <t>과정 전체 일정 구성이 알찼음</t>
-        </is>
-      </c>
+      <c r="AG33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5295,63 +5363,67 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>소방본부</t>
+          <t>△△소방서</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>소방교</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
+          <t>자료가 깔끔하게 정리되어 복습하기 좋았음</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
           <t>강사님이 열정적으로 진행해 주셨음</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -5361,7 +5433,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -5372,12 +5444,12 @@
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5387,32 +5459,28 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>자료가 깔끔하게 정리되어 복습하기 좋았음</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -5436,9 +5504,172 @@
         </is>
       </c>
       <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="inlineStr">
-        <is>
-          <t>교육생 질문에 담당자가 빠르게 답해 주었음</t>
+      <c r="AG34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026/10/21 오후 05:36:00</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>○○소방서</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>소방교</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>실습 장비가 충분해서 직접 해 볼 수 있었음</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>핵심만 짚어 주어 집중이 잘 됐음</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>실습 순서를 단계별로 알려 주어 따라가기 쉬웠음</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>질문에 성실하게 답변해 주셔서 좋았음</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>교육 운영 안내가 미리 와서 준비하기 좋았음</t>
         </is>
       </c>
     </row>

--- a/samples/survey_leadership16.xlsx
+++ b/samples/survey_leadership16.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG35"/>
+  <dimension ref="A1:AH35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -422,6 +422,38 @@
           <t>신임 관리자 리더십과정 16기 설문 결과(모의)</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr"/>
+      <c r="J1" t="inlineStr"/>
+      <c r="K1" t="inlineStr"/>
+      <c r="L1" t="inlineStr"/>
+      <c r="M1" t="inlineStr"/>
+      <c r="N1" t="inlineStr"/>
+      <c r="O1" t="inlineStr"/>
+      <c r="P1" t="inlineStr"/>
+      <c r="Q1" t="inlineStr"/>
+      <c r="R1" t="inlineStr"/>
+      <c r="S1" t="inlineStr"/>
+      <c r="T1" t="inlineStr"/>
+      <c r="U1" t="inlineStr"/>
+      <c r="V1" t="inlineStr"/>
+      <c r="W1" t="inlineStr"/>
+      <c r="X1" t="inlineStr"/>
+      <c r="Y1" t="inlineStr"/>
+      <c r="Z1" t="inlineStr"/>
+      <c r="AA1" t="inlineStr"/>
+      <c r="AB1" t="inlineStr"/>
+      <c r="AC1" t="inlineStr"/>
+      <c r="AD1" t="inlineStr"/>
+      <c r="AE1" t="inlineStr"/>
+      <c r="AF1" t="inlineStr"/>
+      <c r="AG1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -431,160 +463,165 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>소속 기관</t>
+          <t>소속</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>현재 계급</t>
+          <t>근무기간</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>보직</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>팀을 이끄는 방법을 다룬 강의 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>팀을 이끄는 방법을 다룬 강의 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>팀을 이끄는 방법을 다룬 강의 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>팀을 이끄는 방법을 다룬 강의 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>팀을 이끄는 방법을 다룬 강의 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>스트레스 관리 | 이우람 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>스트레스 관리 | 이우람 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>스트레스 관리 | 이우람 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>스트레스 관리 | 이우람 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>스트레스 관리 | 이우람 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>성인지 교육 | 이나래 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>성인지 교육 | 이나래 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>성인지 교육 | 이나래 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>성인지 교육 | 이나래 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>성인지 교육 | 이나래 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>공직가치 | 박바다 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>공직가치 | 박바다 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>공직가치 | 박바다 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>공직가치 | 박바다 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>공직가치 | 박바다 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>공통 | 교육시설환경 | 교재의 품질</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>공통 | 교육시설환경 | 강의실 및 교육기자재</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>공통 | 교육시설환경 | 편의시설</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>공통 | 교육시설환경 | 교직원의 친절도</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>공통 | 구내식당 | 구내식당 이용</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>공통 | 구내식당 | 음식의 간</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>공통 | 구내식당 | 메뉴의 다양성</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>공통 | 구내식당 | 청결도</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>공통 | 구내식당 | 친절도</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>공통 | 과정 운영 | 의견: 이번 과정 운영(일정·시설·안내 등)에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
@@ -598,17 +635,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>5년 미만</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>화재진압</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -626,20 +663,20 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -649,14 +686,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>설명 속도가 빨라 따라가기 어려웠음</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>만족</t>
@@ -664,7 +701,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -674,17 +711,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
           <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -694,19 +731,19 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -719,17 +756,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -739,15 +776,20 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>강의실 의자가 불편했음</t>
         </is>
@@ -761,17 +803,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>예방·안전</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -789,15 +831,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -807,18 +849,18 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -831,12 +873,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
           <t>만족</t>
@@ -854,14 +896,14 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
           <t>강사님이 열정적으로 진행해 주셨음</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
           <t>만족</t>
@@ -869,7 +911,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -884,7 +926,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -897,8 +939,13 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>교육생 질문에 담당자가 빠르게 답해 주었음</t>
         </is>
@@ -917,43 +964,43 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -961,12 +1008,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -974,20 +1021,20 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1000,18 +1047,18 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1024,20 +1071,20 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1046,6 +1093,11 @@
         </is>
       </c>
       <c r="AG5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>강의실 의자가 불편했음</t>
         </is>
@@ -1059,27 +1111,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>5년 이상~10년 미만</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1087,12 +1139,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1100,7 +1152,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1110,14 +1162,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>사례가 조금 더 있으면 좋겠음</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1125,23 +1177,23 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1156,14 +1208,14 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
           <t>점심 직후 시간이라 집중이 어려웠음, 시간 조정 필요</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1191,20 +1243,25 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>쉬는 시간이 짧아 이동하기 바빴음</t>
         </is>
@@ -1218,17 +1275,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>5년 미만</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>행정</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1238,20 +1295,20 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -1264,15 +1321,15 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -1290,14 +1347,14 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
           <t>실습 시간이 부족했음</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1310,22 +1367,22 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
           <t>교구가 부족해 기다리는 시간이 길었음</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1335,12 +1392,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1350,7 +1407,7 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -1360,10 +1417,15 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
         <is>
           <t>강의실 의자가 불편했음</t>
         </is>
@@ -1377,22 +1439,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1402,22 +1464,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1430,36 +1492,36 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1469,19 +1531,19 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
           <t>점심 직후 시간이라 집중이 어려웠음, 시간 조정 필요</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1497,15 +1559,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -1519,6 +1581,11 @@
         </is>
       </c>
       <c r="AG8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>과정 전체 일정 구성이 알찼음</t>
         </is>
@@ -1532,27 +1599,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>상황·통신</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1560,20 +1627,20 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1581,12 +1648,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1602,33 +1669,33 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -1636,7 +1703,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1646,17 +1713,17 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -1664,8 +1731,13 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
       <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1675,27 +1747,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>화재진압</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1703,12 +1775,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -1721,15 +1793,15 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1737,23 +1809,23 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1763,19 +1835,19 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
           <t>이론 비중이 높아 실무 내용이 더 필요함</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="Y10" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1793,12 +1865,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -1808,7 +1880,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1817,6 +1889,11 @@
         </is>
       </c>
       <c r="AG10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
         <is>
           <t>강의실 의자가 불편했음</t>
         </is>
@@ -1830,27 +1907,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>5년 이상~10년 미만</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>예방·안전</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1858,12 +1935,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1871,7 +1948,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1879,20 +1956,20 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1902,17 +1979,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
           <t>설명 속도가 빨라 따라가기 어려웠음</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1922,18 +1999,18 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1943,7 +2020,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1971,7 +2048,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1981,17 +2063,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>5년 미만</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2001,27 +2083,27 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>자료 글씨가 작아 화면이 잘 안 보였음</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2034,12 +2116,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2047,24 +2129,24 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
           <t>설명 속도가 빨라 따라가기 어려웠음</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2077,19 +2159,19 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
           <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="Y12" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2097,7 +2179,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2112,21 +2194,26 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
           <t>불만족</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr">
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr">
         <is>
           <t>식당 대기 시간이 길었음</t>
         </is>
@@ -2140,17 +2227,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>구급</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2168,15 +2255,15 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2186,65 +2273,65 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
           <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
           <t>교구가 부족해 기다리는 시간이 길었음</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="Y13" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2257,35 +2344,40 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2295,40 +2387,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2341,48 +2433,48 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
           <t>이론 비중이 높아 실무 내용이 더 필요함</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -2390,15 +2482,15 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2408,35 +2500,40 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
         <is>
           <t>쉬는 시간이 짧아 이동하기 바빴음</t>
         </is>
@@ -2450,22 +2547,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2475,18 +2572,18 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2496,27 +2593,27 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
           <t>실습 순서를 단계별로 알려 주어 따라가기 쉬웠음</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2524,20 +2621,20 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2547,14 +2644,14 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
           <t>사례가 조금 더 있으면 좋겠음</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="Y15" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2562,22 +2659,22 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -2592,10 +2689,15 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
         <is>
           <t>강의실이 더워서 집중하기 어려웠음</t>
         </is>
@@ -2614,17 +2716,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>5년 미만</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>상황·통신</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2637,12 +2739,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2650,28 +2752,28 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2679,15 +2781,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2697,15 +2799,15 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2713,12 +2815,12 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2731,18 +2833,23 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
           <t>만족</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2752,17 +2859,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>화재진압</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2772,7 +2879,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2780,54 +2887,54 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2835,28 +2942,28 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2866,12 +2973,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -2890,6 +2997,11 @@
         </is>
       </c>
       <c r="AG17" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
         <is>
           <t>교육 운영 안내가 미리 와서 준비하기 좋았음</t>
         </is>
@@ -2903,22 +3015,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>5년 이상~10년 미만</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>행정</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2928,23 +3040,23 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2952,12 +3064,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2970,40 +3082,40 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
           <t>강의실이 더워서 집중하기 어려웠음</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="Y18" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -3016,7 +3128,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -3031,20 +3143,25 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
         <is>
           <t>강의실 의자가 불편했음</t>
         </is>
@@ -3058,22 +3175,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3083,22 +3200,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>실습 장비가 충분해서 직접 해 볼 수 있었음</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -3108,15 +3225,15 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3129,36 +3246,36 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3171,17 +3288,17 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -3191,15 +3308,20 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
         <is>
           <t>강의실 의자가 불편했음</t>
         </is>
@@ -3218,17 +3340,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>구급</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3238,27 +3360,27 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>최신 법령 개정 내용을 알려 주어 실무에 도움이 됨</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -3268,14 +3390,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
           <t>실습 시간이 부족했음</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="O20" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3291,12 +3413,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3312,41 +3434,41 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -3354,7 +3476,12 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3364,27 +3491,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>행정</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3394,14 +3521,14 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>핵심만 짚어 주어 집중이 잘 됐음</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3414,15 +3541,15 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -3430,7 +3557,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -3440,14 +3567,14 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
           <t>강사님이 열정적으로 진행해 주셨음</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="T21" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3455,53 +3582,53 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -3509,7 +3636,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3524,12 +3656,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>상황·통신</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3539,20 +3671,20 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3565,18 +3697,18 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3591,17 +3723,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
           <t>자료가 깔끔하게 정리되어 복습하기 좋았음</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3611,38 +3743,38 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -3660,7 +3792,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3675,22 +3812,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>5년 미만</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>상황·통신</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3700,14 +3837,14 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3715,7 +3852,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -3723,12 +3860,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3741,40 +3878,40 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
           <t>강의실 의자가 불편했음</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3792,17 +3929,17 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
@@ -3812,10 +3949,15 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
         <is>
           <t>과정 전체 일정 구성이 알찼음</t>
         </is>
@@ -3829,17 +3971,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>5년 이상~10년 미만</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>화재진압</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3849,7 +3991,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3857,15 +3999,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3875,15 +4017,15 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3891,41 +4033,41 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
           <t>불만족</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3938,20 +4080,20 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3963,6 +4105,11 @@
         </is>
       </c>
       <c r="AG24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
         <is>
           <t>현장 실습과 이론 비율이 적절했음</t>
         </is>
@@ -3981,17 +4128,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>예방·안전</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4004,12 +4151,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4022,18 +4169,18 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -4046,20 +4193,20 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -4069,14 +4216,14 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
           <t>점심 직후 시간이라 집중이 어려웠음, 시간 조정 필요</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="Y25" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4084,7 +4231,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4099,7 +4246,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -4107,13 +4254,18 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
         <is>
           <t>강의실 의자가 불편했음</t>
         </is>
@@ -4127,44 +4279,44 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>예방·안전</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
           <t>실습 장비가 충분해서 직접 해 볼 수 있었음</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4180,12 +4332,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4198,18 +4350,18 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -4224,17 +4376,17 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
           <t>최신 법령 개정 내용을 알려 주어 실무에 도움이 됨</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -4244,12 +4396,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4272,7 +4424,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AG26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4287,17 +4444,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>5년 이상~10년 미만</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>구급</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4307,64 +4464,64 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
           <t>설명 속도가 빨라 따라가기 어려웠음</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4377,20 +4534,20 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4400,26 +4557,31 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
         <is>
           <t>과정 전체 일정 구성이 알찼음</t>
         </is>
@@ -4433,43 +4595,43 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>5년 이상~10년 미만</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>행정</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -4479,23 +4641,23 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -4503,12 +4665,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4524,20 +4686,20 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4570,7 +4732,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AG28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4585,43 +4752,43 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>5년 미만</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -4631,14 +4798,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
           <t>실습 순서를 단계별로 알려 주어 따라가기 쉬웠음</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="O29" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4654,12 +4821,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4667,33 +4834,33 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4703,17 +4870,17 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -4721,7 +4888,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AG29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4731,22 +4903,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>5년 미만</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>구급</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4756,27 +4928,27 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
           <t>최신 법령 개정 내용을 알려 주어 실무에 도움이 됨</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -4786,14 +4958,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
           <t>설명 속도가 빨라 따라가기 어려웠음</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="O30" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4801,7 +4973,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -4811,17 +4983,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
           <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4831,18 +5003,18 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -4852,22 +5024,22 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
@@ -4880,7 +5052,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AG30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4890,27 +5067,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>화재진압</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4918,15 +5095,15 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4936,27 +5113,27 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
           <t>강의실 의자가 불편했음</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -4966,14 +5143,14 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
           <t>최신 법령 개정 내용을 알려 주어 실무에 도움이 됨</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="T31" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4981,7 +5158,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -4991,14 +5168,14 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
           <t>실습 시간이 부족했음</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="Y31" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -5006,17 +5183,17 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -5040,6 +5217,11 @@
         </is>
       </c>
       <c r="AG31" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
         <is>
           <t>강의실 의자가 불편했음</t>
         </is>
@@ -5053,52 +5235,52 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>5년 이상~10년 미만</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>예방·안전</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
           <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -5108,14 +5290,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
           <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="O32" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -5128,27 +5310,27 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
           <t>자료가 깔끔하게 정리되어 복습하기 좋았음</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -5156,12 +5338,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5174,7 +5356,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -5194,7 +5376,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -5203,6 +5385,11 @@
         </is>
       </c>
       <c r="AG32" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
         <is>
           <t>쉬는 시간이 짧아 이동하기 바빴음</t>
         </is>
@@ -5221,12 +5408,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>5년 이상~10년 미만</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -5244,54 +5431,54 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5304,18 +5491,18 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -5325,7 +5512,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -5335,12 +5522,12 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
@@ -5350,10 +5537,15 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AG33" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5363,17 +5555,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>5년 이상~10년 미만</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -5393,14 +5585,14 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
           <t>자료가 깔끔하게 정리되어 복습하기 좋았음</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="J34" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -5408,27 +5600,27 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
           <t>강사님이 열정적으로 진행해 주셨음</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -5441,41 +5633,41 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5485,12 +5677,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
@@ -5500,11 +5692,16 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr"/>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
       <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5514,22 +5711,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>5년 이상~10년 미만</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>행정</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -5544,14 +5741,14 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
           <t>실습 장비가 충분해서 직접 해 볼 수 있었음</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5559,49 +5756,49 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
           <t>핵심만 짚어 주어 집중이 잘 됐음</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
           <t>실습 순서를 단계별로 알려 주어 따라가기 쉬웠음</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="T35" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5609,65 +5806,70 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
           <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
         <is>
           <t>교육 운영 안내가 미리 와서 준비하기 좋았음</t>
         </is>
